--- a/artfynd/A 57613-2023 artfynd.xlsx
+++ b/artfynd/A 57613-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 57613-2023 artfynd.xlsx
+++ b/artfynd/A 57613-2023 artfynd.xlsx
@@ -3324,7 +3324,7 @@
         <v>119953382</v>
       </c>
       <c r="B25" t="n">
-        <v>95455</v>
+        <v>95478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 57613-2023 artfynd.xlsx
+++ b/artfynd/A 57613-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104947469</v>
+        <v>119953382</v>
       </c>
       <c r="B2" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mellan Busjön, Naren, Bredsjön och Storsjön i Hagfors kommun, Vrm</t>
+          <t>Mellan Busjön, Naren, Bredsjön och Storsjön i Hagfors kommun, Mellan Busjön, Naren, Bredsjön och Storsjön i Hagfors kommun, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>439285.4667834424</v>
+        <v>439282</v>
       </c>
       <c r="R2" t="n">
-        <v>6670753.230070025</v>
+        <v>6671240</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,9 +757,24 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>silverved av tall</t>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,15 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104947471</v>
+        <v>104946950</v>
       </c>
       <c r="B3" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439112.5542976422</v>
+        <v>439139</v>
       </c>
       <c r="R3" t="n">
-        <v>6670849.179019331</v>
+        <v>6671122</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,21 +860,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -891,7 +876,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>silverved av tall</t>
+          <t>björkstubbe</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,15 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104947342</v>
+        <v>104947415</v>
       </c>
       <c r="B4" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439332.5562203875</v>
+        <v>439354</v>
       </c>
       <c r="R4" t="n">
-        <v>6671218.324044776</v>
+        <v>6671078</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,21 +962,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1008,7 +978,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1026,37 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104947091</v>
+        <v>104946943</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439199.4906786011</v>
+        <v>439155</v>
       </c>
       <c r="R5" t="n">
-        <v>6671340.970535801</v>
+        <v>6670997</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,19 +1064,9 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,15 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104947085</v>
+        <v>104946962</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>439421.7598340773</v>
+        <v>439369</v>
       </c>
       <c r="R6" t="n">
-        <v>6671216.350409994</v>
+        <v>6671624</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,19 +1161,9 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,37 +1190,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104947345</v>
+        <v>104947080</v>
       </c>
       <c r="B7" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>439466.2018361838</v>
+        <v>439390</v>
       </c>
       <c r="R7" t="n">
-        <v>6671250.952186655</v>
+        <v>6671670</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,21 +1258,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1346,11 +1271,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1367,19 +1287,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104947090</v>
+        <v>104947085</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1407,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>439147.1221000399</v>
+        <v>439422</v>
       </c>
       <c r="R8" t="n">
-        <v>6671219.408347182</v>
+        <v>6671217</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,19 +1355,9 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,37 +1384,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104946962</v>
+        <v>104947086</v>
       </c>
       <c r="B9" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>439368.6803923168</v>
+        <v>439374</v>
       </c>
       <c r="R9" t="n">
-        <v>6671623.824295259</v>
+        <v>6671140</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,19 +1452,9 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,37 +1481,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104946950</v>
+        <v>104947087</v>
       </c>
       <c r="B10" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>439139.0231490864</v>
+        <v>439367</v>
       </c>
       <c r="R10" t="n">
-        <v>6671121.992804333</v>
+        <v>6671028</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,21 +1549,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1687,11 +1562,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>björkstubbe</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1708,37 +1578,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104947411</v>
+        <v>104947090</v>
       </c>
       <c r="B11" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1748,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>439351.7336740484</v>
+        <v>439147</v>
       </c>
       <c r="R11" t="n">
-        <v>6671292.660334174</v>
+        <v>6671219</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1781,21 +1646,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1804,11 +1659,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1825,37 +1675,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104947415</v>
+        <v>104947091</v>
       </c>
       <c r="B12" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1865,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>439354.6549689775</v>
+        <v>439199</v>
       </c>
       <c r="R12" t="n">
-        <v>6671077.605002012</v>
+        <v>6671341</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1898,21 +1743,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1921,11 +1756,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1942,37 +1772,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104947420</v>
+        <v>104947092</v>
       </c>
       <c r="B13" t="n">
-        <v>77595</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1982,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>439330.080884765</v>
+        <v>439230</v>
       </c>
       <c r="R13" t="n">
-        <v>6671279.581249283</v>
+        <v>6671334</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,21 +1840,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2038,11 +1853,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>lodyta på mossigt block</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2059,15 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104947087</v>
+        <v>104947242</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2075,21 +1880,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2099,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439367.2968860773</v>
+        <v>439143</v>
       </c>
       <c r="R14" t="n">
-        <v>6671028.121588911</v>
+        <v>6670735</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2132,21 +1937,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2155,6 +1950,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2171,15 +1971,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104947300</v>
+        <v>104947420</v>
       </c>
       <c r="B15" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2187,21 +1982,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2211,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>439319.3773465062</v>
+        <v>439330</v>
       </c>
       <c r="R15" t="n">
-        <v>6671506.199899826</v>
+        <v>6671279</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2244,21 +2039,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2270,7 +2055,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>sälg/asp</t>
+          <t>lodyta på mossigt block</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2288,15 +2073,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104947299</v>
+        <v>104947422</v>
       </c>
       <c r="B16" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,21 +2084,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2328,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>439360.4769594357</v>
+        <v>439147</v>
       </c>
       <c r="R16" t="n">
-        <v>6671489.594299268</v>
+        <v>6670718</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2361,21 +2141,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2387,7 +2157,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>sälg/asp</t>
+          <t>lodyta på mossigt block</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2405,15 +2175,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104947242</v>
+        <v>104947469</v>
       </c>
       <c r="B17" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2421,21 +2186,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2445,10 +2210,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>439142.570318472</v>
+        <v>439286</v>
       </c>
       <c r="R17" t="n">
-        <v>6670735.192119633</v>
+        <v>6670753</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2478,21 +2243,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2504,7 +2259,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>silverved av tall</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2522,15 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104947346</v>
+        <v>104947470</v>
       </c>
       <c r="B18" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2538,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2562,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439363.3424954626</v>
+        <v>439179</v>
       </c>
       <c r="R18" t="n">
-        <v>6671030.177914973</v>
+        <v>6670579</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2595,21 +2345,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2621,7 +2361,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>silverved av tall</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2639,15 +2379,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104947092</v>
+        <v>104947471</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2655,21 +2390,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2679,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>439229.2858063132</v>
+        <v>439112</v>
       </c>
       <c r="R19" t="n">
-        <v>6671334.006349982</v>
+        <v>6670849</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2712,21 +2447,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2735,6 +2460,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>silverved av tall</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2751,37 +2481,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104947086</v>
+        <v>104947411</v>
       </c>
       <c r="B20" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2791,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>439373.6350553652</v>
+        <v>439352</v>
       </c>
       <c r="R20" t="n">
-        <v>6671140.002570508</v>
+        <v>6671293</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2824,21 +2549,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2847,6 +2562,11 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2863,15 +2583,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104947348</v>
+        <v>104947299</v>
       </c>
       <c r="B21" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2879,21 +2594,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2903,10 +2618,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439165.3175353098</v>
+        <v>439360</v>
       </c>
       <c r="R21" t="n">
-        <v>6671264.396407674</v>
+        <v>6671490</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2936,21 +2651,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2962,7 +2667,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>sälg/asp</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2980,37 +2685,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104946943</v>
+        <v>104947300</v>
       </c>
       <c r="B22" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3020,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>439154.3851188465</v>
+        <v>439319</v>
       </c>
       <c r="R22" t="n">
-        <v>6670996.312372931</v>
+        <v>6671506</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3053,21 +2753,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3076,6 +2766,11 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>sälg/asp</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3092,15 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104947080</v>
+        <v>104947342</v>
       </c>
       <c r="B23" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3108,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3132,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439390.3841804633</v>
+        <v>439333</v>
       </c>
       <c r="R23" t="n">
-        <v>6671670.243187405</v>
+        <v>6671219</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3165,21 +2855,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3188,6 +2868,11 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3204,37 +2889,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>104947422</v>
+        <v>104947343</v>
       </c>
       <c r="B24" t="n">
-        <v>77595</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6450</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3244,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439146.7837300227</v>
+        <v>439391</v>
       </c>
       <c r="R24" t="n">
-        <v>6670718.695925048</v>
+        <v>6671708</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3277,21 +2957,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3303,7 +2973,7 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>lodyta på mossigt block</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3321,15 +2991,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119953382</v>
+        <v>104947345</v>
       </c>
       <c r="B25" t="n">
-        <v>95478</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3337,34 +3002,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mellan Busjön, Naren, Bredsjön och Storsjön i Hagfors kommun, Mellan Busjön, Naren, Bredsjön och Storsjön i Hagfors kommun, Vrm</t>
+          <t>Mellan Busjön, Naren, Bredsjön och Storsjön i Hagfors kommun, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>439282</v>
+        <v>439466</v>
       </c>
       <c r="R25" t="n">
-        <v>6671240</v>
+        <v>6671251</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3391,12 +3056,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3408,24 +3073,9 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3440,6 +3090,210 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>104947346</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mellan Busjön, Naren, Bredsjön och Storsjön i Hagfors kommun, Vrm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>439363</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6671030</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-05-17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>104947348</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Mellan Busjön, Naren, Bredsjön och Storsjön i Hagfors kommun, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>439165</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6671265</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2022-05-17</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57613-2023 artfynd.xlsx
+++ b/artfynd/A 57613-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119953382</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104946950</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947415</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104946943</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104946962</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947080</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947085</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,6 +1518,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947086</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1575,6 +1620,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947087</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1672,6 +1722,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947090</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1769,6 +1824,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947091</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1866,6 +1926,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947092</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1968,6 +2033,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947242</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2070,6 +2140,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947420</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2172,6 +2247,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947422</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2274,6 +2354,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947469</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2376,6 +2461,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947470</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2478,6 +2568,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947471</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2580,6 +2675,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947411</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2682,6 +2782,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947299</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2784,6 +2889,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947300</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2886,6 +2996,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947342</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2988,6 +3103,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947343</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3090,6 +3210,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947345</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3192,6 +3317,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947346</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3294,8 +3424,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947348</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>